--- a/src/nodes/P/compressor_blade_strength.xlsx
+++ b/src/nodes/P/compressor_blade_strength.xlsx
@@ -1183,28 +1183,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>605.95607802154677</v>
+        <v>633.88010496534787</v>
       </c>
       <c r="C3">
-        <v>2192.9148161599196</v>
+        <v>2171.8555823311617</v>
       </c>
       <c r="D3">
-        <v>342.44132302085274</v>
+        <v>286.24026968149218</v>
       </c>
       <c r="E3">
-        <v>156.1580598103269</v>
+        <v>131.795259321182</v>
       </c>
       <c r="F3">
         <v>2310.3654248608714</v>
       </c>
       <c r="G3">
-        <v>311.48991489418455</v>
+        <v>298.3782062802938</v>
       </c>
       <c r="H3">
-        <v>421.39869012439181</v>
+        <v>349.50150406341515</v>
       </c>
       <c r="I3">
-        <v>182.39482187098957</v>
+        <v>151.275421759076</v>
       </c>
       <c r="J3">
         <v>85.50867723887994</v>
@@ -1255,34 +1255,34 @@
         <v>63.458532650130032</v>
       </c>
       <c r="Z3">
-        <v>53.810997960002794</v>
+        <v>59.574570664650714</v>
       </c>
       <c r="AA3">
         <v>17.23307284756255</v>
       </c>
       <c r="AB3">
-        <v>3.0828977864260882</v>
+        <v>3.1614834824722093</v>
       </c>
       <c r="AC3">
         <v>2.2450542964408755</v>
       </c>
       <c r="AD3">
-        <v>0.46901034702844457</v>
+        <v>-4.0120804813246885E-05</v>
       </c>
       <c r="AE3">
         <v>129826.54201254154</v>
       </c>
       <c r="AF3">
-        <v>519.56080375687441</v>
+        <v>478.55130706716443</v>
       </c>
       <c r="AG3">
         <v>2603402.6141101564</v>
       </c>
       <c r="AH3">
-        <v>251993.85283125105</v>
+        <v>230744.39576792475</v>
       </c>
       <c r="AI3">
-        <v>251993.85283125105</v>
+        <v>230744.39576792475</v>
       </c>
       <c r="AJ3">
         <v>49.178660381553357</v>
@@ -1300,85 +1300,85 @@
         <v>-14.943992214829382</v>
       </c>
       <c r="AO3">
-        <v>-12.133748082611316</v>
+        <v>-17.872488636653454</v>
       </c>
       <c r="AP3">
         <v>-16.660451628313727</v>
       </c>
       <c r="AQ3">
-        <v>-2.9836747294476669</v>
+        <v>-3.1614959975069752</v>
       </c>
       <c r="AR3">
         <v>34617.317468734174</v>
       </c>
       <c r="AS3">
-        <v>3860.4420014278494</v>
+        <v>3875.7820351241721</v>
       </c>
       <c r="AT3">
         <v>-0.32230055803669655</v>
       </c>
       <c r="AU3">
-        <v>-1.5154648573817424</v>
+        <v>-4.24330160066888</v>
       </c>
       <c r="AV3">
         <v>-2.7921140811038363</v>
       </c>
       <c r="AW3">
-        <v>1.2215138678442337</v>
+        <v>3.4202388299638544</v>
       </c>
       <c r="AX3">
         <v>233.0300165549655</v>
       </c>
       <c r="AY3">
-        <v>0.15985706407900163</v>
+        <v>0.44759977942120455</v>
       </c>
       <c r="AZ3">
         <v>-396.165191411757</v>
       </c>
       <c r="BA3">
-        <v>0.19668331475880332</v>
+        <v>0.55071328132464925</v>
       </c>
       <c r="BB3">
-        <v>-0.057446812086722532</v>
+        <v>-0.068944670673709477</v>
       </c>
       <c r="BC3">
-        <v>-0.078906471256483326</v>
+        <v>-0.094689948213048089</v>
       </c>
       <c r="BD3">
-        <v>-19.93083977526733</v>
+        <v>-19.930810996176966</v>
       </c>
       <c r="BE3">
-        <v>0.31328779157916881</v>
+        <v>1.1934992119602346</v>
       </c>
       <c r="BF3">
-        <v>-0.57574766713996706</v>
+        <v>-0.57574683579044406</v>
       </c>
       <c r="BG3">
-        <v>0.081153347586440619</v>
+        <v>0.30793765003918683</v>
       </c>
       <c r="BH3">
         <v>4.1291689043533868</v>
       </c>
       <c r="BI3">
-        <v>45.097924142723919</v>
+        <v>45.111170099919228</v>
       </c>
       <c r="BJ3">
         <v>203.89916603090629</v>
       </c>
       <c r="BK3">
-        <v>0.25215625649625695</v>
+        <v>0.70605407663844821</v>
       </c>
       <c r="BL3">
         <v>-411.91622642695495</v>
       </c>
       <c r="BM3">
-        <v>0.025609169261465947</v>
+        <v>0.071542446334337262</v>
       </c>
       <c r="BN3">
         <v>-5.752748831502899</v>
       </c>
       <c r="BO3">
-        <v>0.011997611689346065</v>
+        <v>0.012040535220523532</v>
       </c>
       <c r="BP3">
         <v>7.2164411153935655</v>
@@ -1393,40 +1393,40 @@
         <v>-22.714179712373966</v>
       </c>
       <c r="BT3">
-        <v>-0.17139838455151263</v>
+        <v>0.00038729554440985808</v>
       </c>
       <c r="BU3">
-        <v>2.6975169378248611</v>
+        <v>2.6652389894464097</v>
       </c>
       <c r="BV3">
-        <v>65.309617898670368</v>
+        <v>59.5735316456726</v>
       </c>
       <c r="BW3">
-        <v>-3.6313048257120446</v>
+        <v>-3.3348119169915713</v>
       </c>
       <c r="BX3">
         <v>26.782931118850406</v>
       </c>
       <c r="BY3">
-        <v>1.3091919520489834</v>
+        <v>3.9322905787931246</v>
       </c>
       <c r="BZ3">
         <v>-45.067399859569377</v>
       </c>
       <c r="CA3">
-        <v>-1.7690030421071203</v>
+        <v>-4.9386486773687173</v>
       </c>
       <c r="CB3">
-        <v>209.17854534166438</v>
+        <v>178.05928370635184</v>
       </c>
       <c r="CC3">
-        <v>1.3117047812424536</v>
+        <v>3.9443294477486059</v>
       </c>
       <c r="CD3">
-        <v>1.09953915027149</v>
+        <v>1.2917046233843481</v>
       </c>
       <c r="CE3">
-        <v>175.34433303059456</v>
+        <v>58.311559175484767</v>
       </c>
     </row>
   </sheetData>
@@ -2278,28 +2278,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>605.95607802154677</v>
+        <v>633.88010496534787</v>
       </c>
       <c r="C3">
-        <v>752.15876540066176</v>
+        <v>611.17995943786332</v>
       </c>
       <c r="D3">
-        <v>117.42551993385635</v>
+        <v>80.528333728590184</v>
       </c>
       <c r="E3">
-        <v>156.11799707114471</v>
+        <v>131.75879294644514</v>
       </c>
       <c r="F3">
-        <v>1151.8711609832421</v>
+        <v>892.70014976201276</v>
       </c>
       <c r="G3">
-        <v>649.75418237927045</v>
+        <v>779.70501885512442</v>
       </c>
       <c r="H3">
-        <v>149.30692182165765</v>
+        <v>105.93078979915029</v>
       </c>
       <c r="I3">
-        <v>129.62119973053984</v>
+        <v>118.66334942073287</v>
       </c>
       <c r="J3">
         <v>89.397764756258482</v>
@@ -2350,34 +2350,34 @@
         <v>82.768355519594664</v>
       </c>
       <c r="Z3">
-        <v>60.200378024019521</v>
+        <v>60.200378024019528</v>
       </c>
       <c r="AA3">
-        <v>3.6158868735800045</v>
+        <v>3.6158868735800058</v>
       </c>
       <c r="AB3">
-        <v>2.7199172286965267</v>
+        <v>2.7199172286965263</v>
       </c>
       <c r="AC3">
-        <v>-3.3111571687938093E-05</v>
+        <v>-3.3060976490015982E-05</v>
       </c>
       <c r="AD3">
-        <v>0.37060802963876138</v>
+        <v>0.37104497139144288</v>
       </c>
       <c r="AE3">
-        <v>7865.5434356740225</v>
+        <v>4065.8766397749409</v>
       </c>
       <c r="AF3">
-        <v>2206.1906981106</v>
+        <v>3573.9466585398786</v>
       </c>
       <c r="AG3">
-        <v>1719391.5132254697</v>
+        <v>1332528.4227497396</v>
       </c>
       <c r="AH3">
-        <v>657870.56154020235</v>
+        <v>789444.71265988413</v>
       </c>
       <c r="AI3">
-        <v>657870.56154020235</v>
+        <v>789444.71265988413</v>
       </c>
       <c r="AJ3">
         <v>57.9376826296774</v>
@@ -2392,136 +2392,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-24.830670800270592</v>
+        <v>-24.830670803463626</v>
       </c>
       <c r="AO3">
-        <v>-13.564009879411225</v>
+        <v>-13.564029952641777</v>
       </c>
       <c r="AP3">
-        <v>-3.6159012233729184</v>
+        <v>-3.6159012014461265</v>
       </c>
       <c r="AQ3">
-        <v>-2.63223640897859</v>
+        <v>-2.6321329687830652</v>
       </c>
       <c r="AR3">
-        <v>20848.682238261583</v>
+        <v>16133.226795616853</v>
       </c>
       <c r="AS3">
-        <v>9024.0458406210855</v>
+        <v>10841.522156159283</v>
       </c>
       <c r="AT3">
         <v>-3.9599041363713927</v>
       </c>
       <c r="AU3">
-        <v>-0.81120722567163961</v>
+        <v>-2.2713802318805905</v>
       </c>
       <c r="AV3">
         <v>-2.5163780046624584</v>
       </c>
       <c r="AW3">
-        <v>0.80907945747682986</v>
+        <v>2.2654224809351238</v>
       </c>
       <c r="AX3">
         <v>37.216050625688226</v>
       </c>
       <c r="AY3">
-        <v>32.366521974845043</v>
+        <v>90.626261529566122</v>
       </c>
       <c r="AZ3">
         <v>-83.160971047292918</v>
       </c>
       <c r="BA3">
-        <v>37.57661158228224</v>
+        <v>105.21451243039027</v>
       </c>
       <c r="BB3">
-        <v>-1.2211598420538306</v>
+        <v>-1.5967487140540819</v>
       </c>
       <c r="BC3">
-        <v>-1.3719316478932893</v>
+        <v>-1.7557725744527606</v>
       </c>
       <c r="BD3">
-        <v>-9.7790016874646941</v>
+        <v>-9.7789532667252246</v>
       </c>
       <c r="BE3">
-        <v>-4.0489823547640418</v>
+        <v>-13.115050157848284</v>
       </c>
       <c r="BF3">
-        <v>-0.46904651218282906</v>
+        <v>-0.60613746962151516</v>
       </c>
       <c r="BG3">
-        <v>-0.44868814124789153</v>
+        <v>-1.2097056085798217</v>
       </c>
       <c r="BH3">
         <v>57.031373352670236</v>
       </c>
       <c r="BI3">
-        <v>43.009795756683864</v>
+        <v>41.878122340015913</v>
       </c>
       <c r="BJ3">
         <v>-49.517229058193337</v>
       </c>
       <c r="BK3">
-        <v>49.299486985543993</v>
+        <v>137.71304693606885</v>
       </c>
       <c r="BL3">
         <v>-76.4776147385684</v>
       </c>
       <c r="BM3">
-        <v>5.3994505013022227</v>
+        <v>17.841793866485638</v>
       </c>
       <c r="BN3">
-        <v>0.40480639183012262</v>
+        <v>0.27000706893494908</v>
       </c>
       <c r="BO3">
-        <v>0.021044197706035783</v>
+        <v>0.033605654553080483</v>
       </c>
       <c r="BP3">
-        <v>-3.2687993695740043</v>
+        <v>-1.6327255692881058</v>
       </c>
       <c r="BQ3">
-        <v>5.9797572819461813</v>
+        <v>4.85840254039265</v>
       </c>
       <c r="BR3">
-        <v>82.737112974032357</v>
+        <v>82.748291849059726</v>
       </c>
       <c r="BS3">
-        <v>-4.6474526211739606</v>
+        <v>-4.3522229196209352</v>
       </c>
       <c r="BT3">
-        <v>-1.5218337180137027</v>
+        <v>-1.5161965513964972</v>
       </c>
       <c r="BU3">
-        <v>4.13160435468437</v>
+        <v>4.7973998344818662</v>
       </c>
       <c r="BV3">
-        <v>-46.895523473635045</v>
+        <v>-42.900851961620013</v>
       </c>
       <c r="BW3">
-        <v>-3.4630793257187165</v>
+        <v>-3.9523207460992236</v>
       </c>
       <c r="BX3">
-        <v>-37.790728614544264</v>
+        <v>-59.262897779175809</v>
       </c>
       <c r="BY3">
-        <v>92.337227008446334</v>
+        <v>184.89000510444936</v>
       </c>
       <c r="BZ3">
-        <v>32.9379634557638</v>
+        <v>57.753725136563276</v>
       </c>
       <c r="CA3">
-        <v>-77.000998139437755</v>
+        <v>-151.3231629736859</v>
       </c>
       <c r="CB3">
-        <v>162.55983987584969</v>
+        <v>176.41811584411241</v>
       </c>
       <c r="CC3">
-        <v>92.338317142221328</v>
+        <v>184.89396251685108</v>
       </c>
       <c r="CD3">
-        <v>1.4148635983872508</v>
+        <v>1.3037209863596655</v>
       </c>
       <c r="CE3">
-        <v>2.4908402829753697</v>
+        <v>1.2439562485932334</v>
       </c>
     </row>
   </sheetData>
@@ -3373,10 +3373,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>605.95607802154677</v>
+        <v>633.88010496534787</v>
       </c>
       <c r="C3">
-        <v>701.28049855759764</v>
+        <v>467.52167377493544</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>701.28049855759764</v>
+        <v>467.52167377493544</v>
       </c>
       <c r="G3">
-        <v>1046.60611404446</v>
+        <v>1345.6364323428768</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -3442,37 +3442,37 @@
         <v>79.5589226239994</v>
       </c>
       <c r="Y3">
-        <v>91.332059899452346</v>
+        <v>91.331797851456244</v>
       </c>
       <c r="Z3">
         <v>64.573197552003322</v>
       </c>
       <c r="AA3">
-        <v>0.553839824277081</v>
+        <v>0.55383823521168141</v>
       </c>
       <c r="AB3">
-        <v>2.6369830744030627</v>
+        <v>2.6369830744030622</v>
       </c>
       <c r="AC3">
-        <v>-4.5795167389976518E-06</v>
+        <v>7.6332190110594088E-16</v>
       </c>
       <c r="AD3">
-        <v>0.33581097998823356</v>
+        <v>0.33696820109109316</v>
       </c>
       <c r="AE3">
-        <v>1234.1839301325151</v>
+        <v>372.61799113156627</v>
       </c>
       <c r="AF3">
-        <v>7059.7717556697708</v>
+        <v>14429.820466879384</v>
       </c>
       <c r="AG3">
-        <v>1274619.2944687926</v>
+        <v>849757.3856558284</v>
       </c>
       <c r="AH3">
-        <v>1219409.6049019767</v>
+        <v>1567812.5336796751</v>
       </c>
       <c r="AI3">
-        <v>1219409.6049019767</v>
+        <v>1567812.5336796751</v>
       </c>
       <c r="AJ3">
         <v>63.932258496019372</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-27.399801359165782</v>
+        <v>-27.399539355436875</v>
       </c>
       <c r="AO3">
-        <v>-14.545907489135866</v>
+        <v>-14.545959025155376</v>
       </c>
       <c r="AP3">
-        <v>-0.55384201427868573</v>
+        <v>-0.55383823521168107</v>
       </c>
       <c r="AQ3">
-        <v>-2.551773721409837</v>
+        <v>-2.551479932564138</v>
       </c>
       <c r="AR3">
-        <v>13969.136602849687</v>
+        <v>9307.97809109926</v>
       </c>
       <c r="AS3">
-        <v>15633.832573848667</v>
+        <v>20168.878674648146</v>
       </c>
       <c r="AT3">
         <v>-6.1436186227014788</v>
       </c>
       <c r="AU3">
-        <v>-0.55821745886440266</v>
+        <v>-1.5630088848203272</v>
       </c>
       <c r="AV3">
         <v>-2.43534800153578</v>
       </c>
       <c r="AW3">
-        <v>0.59203895885166213</v>
+        <v>1.6577090847846538</v>
       </c>
       <c r="AX3">
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>87.464873101602251</v>
+        <v>244.90164468448626</v>
       </c>
       <c r="AZ3">
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>97.940153087405932</v>
+        <v>274.23242864473661</v>
       </c>
       <c r="BB3">
-        <v>-2.4469522903070722</v>
+        <v>-3.3983311221023365</v>
       </c>
       <c r="BC3">
-        <v>-2.4167853486053765</v>
+        <v>-3.2117770952087716</v>
       </c>
       <c r="BD3">
         <v>0</v>
       </c>
       <c r="BE3">
-        <v>-6.0191573727739156</v>
+        <v>-18.562657983093324</v>
       </c>
       <c r="BF3">
         <v>0</v>
       </c>
       <c r="BG3">
-        <v>-0.38500843247115224</v>
+        <v>-0.92036142824470424</v>
       </c>
       <c r="BH3">
         <v>70.641360541900085</v>
       </c>
       <c r="BI3">
-        <v>41.249517962932657</v>
+        <v>39.66135793772532</v>
       </c>
       <c r="BJ3">
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>130.33586909607223</v>
+        <v>363.56118739215361</v>
       </c>
       <c r="BL3">
         <v>0</v>
       </c>
       <c r="BM3">
-        <v>15.966804327586004</v>
+        <v>54.804228956935958</v>
       </c>
       <c r="BN3">
         <v>90</v>
       </c>
       <c r="BO3">
-        <v>0.040636627630376475</v>
+        <v>0.079492418135408874</v>
       </c>
       <c r="BP3">
-        <v>-0.30725127003462976</v>
+        <v>-0.38944099907906726</v>
       </c>
       <c r="BQ3">
-        <v>91.332059874894753</v>
+        <v>91.331797851456244</v>
       </c>
       <c r="BR3">
-        <v>-0.80042837856141813</v>
+        <v>-0.71823547134429844</v>
       </c>
       <c r="BS3">
-        <v>-91.331535867436827</v>
+        <v>-91.331797851456258</v>
       </c>
       <c r="BT3">
-        <v>-3.0545195262975025</v>
+        <v>-3.0400874167888978</v>
       </c>
       <c r="BU3">
-        <v>5.7781211268123265</v>
+        <v>7.2105100424183926</v>
       </c>
       <c r="BV3">
-        <v>-40.299011839278151</v>
+        <v>-34.592355869996027</v>
       </c>
       <c r="BW3">
-        <v>-4.7638657008011149</v>
+        <v>-6.017983628334159</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3">
-        <v>106.71432789737916</v>
+        <v>181.77599917345981</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>-87.42171343011114</v>
+        <v>-150.41466813048263</v>
       </c>
       <c r="CB3">
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>106.71502241991253</v>
+        <v>181.77832912827716</v>
       </c>
       <c r="CD3">
         <v>1E+307</v>
       </c>
       <c r="CE3">
-        <v>2.1552729389398793</v>
+        <v>1.2652773358792058</v>
       </c>
     </row>
   </sheetData>
